--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -922,6 +922,286 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardFire</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火抗寶石</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🧯</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resFire</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火焰抗性%</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardIce</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰抗寶石</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🧊</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resIce</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰霜抗性%</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardLightning</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電抗寶石</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔌</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLightning</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷電抗性%</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardPoison</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毒抗寶石</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💊</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resPoison</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">劇毒抗性%</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardDark</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗抗寶石</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕯️</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resDark</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗影抗性%</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardLight</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖抗寶石</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕶️</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖光抗性%</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardAll</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全屬性抗性寶石</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌈</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resAll</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全屬性抗性%</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -440,27 +440,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">sunstone</t>
+          <t xml:space="preserve">catseye</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">太陽石</t>
+          <t xml:space="preserve">貓眼石</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">☀️</t>
+          <t xml:space="preserve">👁️</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">luck</t>
+          <t xml:space="preserve">hit</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">幸運值</t>
+          <t xml:space="preserve">命中率%</t>
         </is>
       </c>
       <c r="F13">
@@ -468,34 +468,34 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FALSE</t>
+          <t xml:space="preserve">TRUE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">jade</t>
+          <t xml:space="preserve">sunstone</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">翡翠</t>
+          <t xml:space="preserve">太陽石</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟩</t>
+          <t xml:space="preserve">☀️</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">tenacity</t>
+          <t xml:space="preserve">luck</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">韌性%</t>
+          <t xml:space="preserve">幸運值</t>
         </is>
       </c>
       <c r="F14">
@@ -503,38 +503,38 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">FALSE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">turquoise</t>
+          <t xml:space="preserve">jade</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">綠松石</t>
+          <t xml:space="preserve">翡翠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟦</t>
+          <t xml:space="preserve">🟩</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockRate</t>
+          <t xml:space="preserve">tenacity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋率%</t>
+          <t xml:space="preserve">韌性%</t>
         </is>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -545,31 +545,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">agate</t>
+          <t xml:space="preserve">turquoise</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">瑪瑙</t>
+          <t xml:space="preserve">綠松石</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
+          <t xml:space="preserve">🟦</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockDmgRed</t>
+          <t xml:space="preserve">blockRate</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋減傷%</t>
+          <t xml:space="preserve">格擋率%</t>
         </is>
       </c>
       <c r="F16">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -580,31 +580,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pearl</t>
+          <t xml:space="preserve">agate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">珍珠</t>
+          <t xml:space="preserve">瑪瑙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">🤍</t>
+          <t xml:space="preserve">🟤</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldEff</t>
+          <t xml:space="preserve">blockDmgRed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾效率%</t>
+          <t xml:space="preserve">格擋減傷%</t>
         </is>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -615,31 +615,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">malachite</t>
+          <t xml:space="preserve">pearl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">孔雀石</t>
+          <t xml:space="preserve">珍珠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">💚</t>
+          <t xml:space="preserve">🤍</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pRes</t>
+          <t xml:space="preserve">shieldEff</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理抗性%</t>
+          <t xml:space="preserve">護盾效率%</t>
         </is>
       </c>
       <c r="F18">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -650,27 +650,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">fluorite</t>
+          <t xml:space="preserve">malachite</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">螢石</t>
+          <t xml:space="preserve">孔雀石</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">💙</t>
+          <t xml:space="preserve">💚</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">mRes</t>
+          <t xml:space="preserve">pRes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法抗性%</t>
+          <t xml:space="preserve">物理抗性%</t>
         </is>
       </c>
       <c r="F19">
@@ -685,38 +685,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">spinel</t>
+          <t xml:space="preserve">fluorite</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">尖晶石</t>
+          <t xml:space="preserve">螢石</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">💙</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsFire</t>
+          <t xml:space="preserve">mRes</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人傷害%</t>
+          <t xml:space="preserve">魔法抗性%</t>
         </is>
       </c>
       <c r="F20">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -725,27 +720,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">aquamarine</t>
+          <t xml:space="preserve">spinel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">海藍寶石</t>
+          <t xml:space="preserve">尖晶石</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsIce</t>
+          <t xml:space="preserve">dmgVsFire</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人傷害%</t>
+          <t xml:space="preserve">對火屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F21">
@@ -765,27 +760,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">amazonite</t>
+          <t xml:space="preserve">aquamarine</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">天河石</t>
+          <t xml:space="preserve">海藍寶石</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLightning</t>
+          <t xml:space="preserve">dmgVsIce</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">對雷屬性敵人傷害%</t>
+          <t xml:space="preserve">對冰屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F22">
@@ -805,27 +800,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">peridot</t>
+          <t xml:space="preserve">amazonite</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">橄欖石</t>
+          <t xml:space="preserve">天河石</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsPoison</t>
+          <t xml:space="preserve">dmgVsLightning</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人傷害%</t>
+          <t xml:space="preserve">對雷屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F23">
@@ -845,27 +840,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">citrine</t>
+          <t xml:space="preserve">peridot</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃水晶</t>
+          <t xml:space="preserve">橄欖石</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLight</t>
+          <t xml:space="preserve">dmgVsPoison</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人傷害%</t>
+          <t xml:space="preserve">對毒屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F24">
@@ -885,27 +880,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">tourmaline</t>
+          <t xml:space="preserve">citrine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">黑碧璽</t>
+          <t xml:space="preserve">黃水晶</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsDark</t>
+          <t xml:space="preserve">dmgVsLight</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人傷害%</t>
+          <t xml:space="preserve">對聖屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F25">
@@ -925,27 +920,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreFire</t>
+          <t xml:space="preserve">tourmaline</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">焰核寶石</t>
+          <t xml:space="preserve">黑碧璽</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgFire</t>
+          <t xml:space="preserve">dmgVsDark</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">火屬性傷害提升%</t>
+          <t xml:space="preserve">對暗屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F26">
@@ -965,27 +960,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreIce</t>
+          <t xml:space="preserve">coreFire</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰核寶石</t>
+          <t xml:space="preserve">焰核寶石</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌨️</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgIce</t>
+          <t xml:space="preserve">elemDmgFire</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰屬性傷害提升%</t>
+          <t xml:space="preserve">火屬性傷害提升%</t>
         </is>
       </c>
       <c r="F27">
@@ -1005,27 +1000,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLightning</t>
+          <t xml:space="preserve">coreIce</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷核寶石</t>
+          <t xml:space="preserve">冰核寶石</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">🌨️</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLightning</t>
+          <t xml:space="preserve">elemDmgIce</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷屬性傷害提升%</t>
+          <t xml:space="preserve">冰屬性傷害提升%</t>
         </is>
       </c>
       <c r="F28">
@@ -1045,27 +1040,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">corePoison</t>
+          <t xml:space="preserve">coreLightning</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒核寶石</t>
+          <t xml:space="preserve">雷核寶石</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦠</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgPoison</t>
+          <t xml:space="preserve">elemDmgLightning</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒屬性傷害提升%</t>
+          <t xml:space="preserve">雷屬性傷害提升%</t>
         </is>
       </c>
       <c r="F29">
@@ -1085,27 +1080,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLight</t>
+          <t xml:space="preserve">corePoison</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖核寶石</t>
+          <t xml:space="preserve">毒核寶石</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🦠</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLight</t>
+          <t xml:space="preserve">elemDmgPoison</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖屬性傷害提升%</t>
+          <t xml:space="preserve">毒屬性傷害提升%</t>
         </is>
       </c>
       <c r="F30">
@@ -1125,27 +1120,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreDark</t>
+          <t xml:space="preserve">coreLight</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗核寶石</t>
+          <t xml:space="preserve">聖核寶石</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌚</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgDark</t>
+          <t xml:space="preserve">elemDmgLight</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗屬性傷害提升%</t>
+          <t xml:space="preserve">聖屬性傷害提升%</t>
         </is>
       </c>
       <c r="F31">
@@ -1165,31 +1160,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardFire</t>
+          <t xml:space="preserve">coreDark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">火抗寶石</t>
+          <t xml:space="preserve">暗核寶石</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧯</t>
+          <t xml:space="preserve">🌚</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">resFire</t>
+          <t xml:space="preserve">elemDmgDark</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰抗性%</t>
+          <t xml:space="preserve">暗屬性傷害提升%</t>
         </is>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1205,27 +1200,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardIce</t>
+          <t xml:space="preserve">wardFire</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰抗寶石</t>
+          <t xml:space="preserve">火抗寶石</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">🧯</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">resIce</t>
+          <t xml:space="preserve">resFire</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜抗性%</t>
+          <t xml:space="preserve">火焰抗性%</t>
         </is>
       </c>
       <c r="F33">
@@ -1245,27 +1240,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLightning</t>
+          <t xml:space="preserve">wardIce</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">電抗寶石</t>
+          <t xml:space="preserve">冰抗寶石</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔌</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLightning</t>
+          <t xml:space="preserve">resIce</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電抗性%</t>
+          <t xml:space="preserve">冰霜抗性%</t>
         </is>
       </c>
       <c r="F34">
@@ -1285,27 +1280,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardPoison</t>
+          <t xml:space="preserve">wardLightning</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒抗寶石</t>
+          <t xml:space="preserve">電抗寶石</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">💊</t>
+          <t xml:space="preserve">🔌</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">resPoison</t>
+          <t xml:space="preserve">resLightning</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">劇毒抗性%</t>
+          <t xml:space="preserve">雷電抗性%</t>
         </is>
       </c>
       <c r="F35">
@@ -1325,27 +1320,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardDark</t>
+          <t xml:space="preserve">wardPoison</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗抗寶石</t>
+          <t xml:space="preserve">毒抗寶石</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕯️</t>
+          <t xml:space="preserve">💊</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">resDark</t>
+          <t xml:space="preserve">resPoison</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影抗性%</t>
+          <t xml:space="preserve">劇毒抗性%</t>
         </is>
       </c>
       <c r="F36">
@@ -1365,27 +1360,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLight</t>
+          <t xml:space="preserve">wardDark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖抗寶石</t>
+          <t xml:space="preserve">暗抗寶石</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕶️</t>
+          <t xml:space="preserve">🕯️</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLight</t>
+          <t xml:space="preserve">resDark</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖光抗性%</t>
+          <t xml:space="preserve">暗影抗性%</t>
         </is>
       </c>
       <c r="F37">
@@ -1405,38 +1400,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t xml:space="preserve">wardLight</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖抗寶石</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕶️</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖光抗性%</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t xml:space="preserve">wardAll</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性寶石</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">🌈</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">resAll</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性%</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="F39">
         <v>1</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>

--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -195,31 +195,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">diamond</t>
+          <t xml:space="preserve">iolite</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">鑽石</t>
+          <t xml:space="preserve">堇青石</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚪</t>
+          <t xml:space="preserve">🔮</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">defFlat</t>
+          <t xml:space="preserve">mpFlat</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理防禦</t>
+          <t xml:space="preserve">法力值</t>
         </is>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -230,31 +230,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">lapis</t>
+          <t xml:space="preserve">kyanite</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">青金石</t>
+          <t xml:space="preserve">藍晶石</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔷</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mdefFlat</t>
+          <t xml:space="preserve">mpRegen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法防禦</t>
+          <t xml:space="preserve">法力恢復/秒</t>
         </is>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -265,62 +265,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">amethyst</t>
+          <t xml:space="preserve">diamond</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">紫水晶</t>
+          <t xml:space="preserve">鑽石</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟣</t>
+          <t xml:space="preserve">⚪</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">critRate</t>
+          <t xml:space="preserve">defFlat</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊率%</t>
+          <t xml:space="preserve">物理防禦</t>
         </is>
       </c>
       <c r="F8">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">FALSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">garnet</t>
+          <t xml:space="preserve">lapis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">石榴石</t>
+          <t xml:space="preserve">青金石</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟠</t>
+          <t xml:space="preserve">🔷</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">critDmg</t>
+          <t xml:space="preserve">mdefFlat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊傷害%</t>
+          <t xml:space="preserve">魔法防禦</t>
         </is>
       </c>
       <c r="F9">
@@ -328,34 +328,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">FALSE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">opal</t>
+          <t xml:space="preserve">amethyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">蛋白石</t>
+          <t xml:space="preserve">紫水晶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">🩵</t>
+          <t xml:space="preserve">🟣</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">aspd</t>
+          <t xml:space="preserve">critRate</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度%</t>
+          <t xml:space="preserve">暴擊率%</t>
         </is>
       </c>
       <c r="F10">
@@ -370,31 +370,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">onyx</t>
+          <t xml:space="preserve">garnet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">黑曜石</t>
+          <t xml:space="preserve">石榴石</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚫</t>
+          <t xml:space="preserve">🟠</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">lifesteal</t>
+          <t xml:space="preserve">critDmg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">吸血%</t>
+          <t xml:space="preserve">暴擊傷害%</t>
         </is>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -405,31 +405,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">moonstone</t>
+          <t xml:space="preserve">opal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">月光石</t>
+          <t xml:space="preserve">蛋白石</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌙</t>
+          <t xml:space="preserve">🩵</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">evasion</t>
+          <t xml:space="preserve">aspd</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃避率%</t>
+          <t xml:space="preserve">攻擊速度%</t>
         </is>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -440,31 +440,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">catseye</t>
+          <t xml:space="preserve">onyx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">貓眼石</t>
+          <t xml:space="preserve">黑曜石</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">👁️</t>
+          <t xml:space="preserve">⚫</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">hit</t>
+          <t xml:space="preserve">lifesteal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">命中率%</t>
+          <t xml:space="preserve">吸血%</t>
         </is>
       </c>
       <c r="F13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -475,62 +475,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">sunstone</t>
+          <t xml:space="preserve">moonstone</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">太陽石</t>
+          <t xml:space="preserve">月光石</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">☀️</t>
+          <t xml:space="preserve">🌙</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">luck</t>
+          <t xml:space="preserve">evasion</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">幸運值</t>
+          <t xml:space="preserve">閃避率%</t>
         </is>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FALSE</t>
+          <t xml:space="preserve">TRUE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">jade</t>
+          <t xml:space="preserve">catseye</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">翡翠</t>
+          <t xml:space="preserve">貓眼石</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟩</t>
+          <t xml:space="preserve">👁️</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">tenacity</t>
+          <t xml:space="preserve">hit</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">韌性%</t>
+          <t xml:space="preserve">命中率%</t>
         </is>
       </c>
       <c r="F15">
@@ -545,62 +545,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">turquoise</t>
+          <t xml:space="preserve">sunstone</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">綠松石</t>
+          <t xml:space="preserve">太陽石</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟦</t>
+          <t xml:space="preserve">☀️</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockRate</t>
+          <t xml:space="preserve">luck</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋率%</t>
+          <t xml:space="preserve">幸運值</t>
         </is>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">FALSE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">agate</t>
+          <t xml:space="preserve">jade</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">瑪瑙</t>
+          <t xml:space="preserve">翡翠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
+          <t xml:space="preserve">🟩</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockDmgRed</t>
+          <t xml:space="preserve">tenacity</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋減傷%</t>
+          <t xml:space="preserve">韌性%</t>
         </is>
       </c>
       <c r="F17">
@@ -615,31 +615,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pearl</t>
+          <t xml:space="preserve">turquoise</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">珍珠</t>
+          <t xml:space="preserve">綠松石</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">🤍</t>
+          <t xml:space="preserve">🟦</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldEff</t>
+          <t xml:space="preserve">blockRate</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾效率%</t>
+          <t xml:space="preserve">格擋率%</t>
         </is>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -650,31 +650,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">malachite</t>
+          <t xml:space="preserve">agate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">孔雀石</t>
+          <t xml:space="preserve">瑪瑙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">💚</t>
+          <t xml:space="preserve">🟤</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pRes</t>
+          <t xml:space="preserve">blockDmgRed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理抗性%</t>
+          <t xml:space="preserve">格擋減傷%</t>
         </is>
       </c>
       <c r="F19">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -685,31 +685,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">fluorite</t>
+          <t xml:space="preserve">pearl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">螢石</t>
+          <t xml:space="preserve">珍珠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">💙</t>
+          <t xml:space="preserve">🤍</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">mRes</t>
+          <t xml:space="preserve">shieldEff</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法抗性%</t>
+          <t xml:space="preserve">護盾效率%</t>
         </is>
       </c>
       <c r="F20">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -720,38 +720,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">spinel</t>
+          <t xml:space="preserve">malachite</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">尖晶石</t>
+          <t xml:space="preserve">孔雀石</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">💚</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsFire</t>
+          <t xml:space="preserve">pRes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人傷害%</t>
+          <t xml:space="preserve">物理抗性%</t>
         </is>
       </c>
       <c r="F21">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -760,38 +755,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">aquamarine</t>
+          <t xml:space="preserve">fluorite</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">海藍寶石</t>
+          <t xml:space="preserve">螢石</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">💙</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsIce</t>
+          <t xml:space="preserve">mRes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人傷害%</t>
+          <t xml:space="preserve">魔法抗性%</t>
         </is>
       </c>
       <c r="F22">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -800,27 +790,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">amazonite</t>
+          <t xml:space="preserve">spinel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">天河石</t>
+          <t xml:space="preserve">尖晶石</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLightning</t>
+          <t xml:space="preserve">dmgVsFire</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">對雷屬性敵人傷害%</t>
+          <t xml:space="preserve">對火屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F23">
@@ -840,27 +830,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">peridot</t>
+          <t xml:space="preserve">aquamarine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">橄欖石</t>
+          <t xml:space="preserve">海藍寶石</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsPoison</t>
+          <t xml:space="preserve">dmgVsIce</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人傷害%</t>
+          <t xml:space="preserve">對冰屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F24">
@@ -880,27 +870,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">citrine</t>
+          <t xml:space="preserve">amazonite</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃水晶</t>
+          <t xml:space="preserve">天河石</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLight</t>
+          <t xml:space="preserve">dmgVsLightning</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人傷害%</t>
+          <t xml:space="preserve">對雷屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F25">
@@ -920,27 +910,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">tourmaline</t>
+          <t xml:space="preserve">peridot</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">黑碧璽</t>
+          <t xml:space="preserve">橄欖石</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsDark</t>
+          <t xml:space="preserve">dmgVsPoison</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人傷害%</t>
+          <t xml:space="preserve">對毒屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F26">
@@ -960,27 +950,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreFire</t>
+          <t xml:space="preserve">citrine</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">焰核寶石</t>
+          <t xml:space="preserve">黃水晶</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgFire</t>
+          <t xml:space="preserve">dmgVsLight</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">火屬性傷害提升%</t>
+          <t xml:space="preserve">對聖屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F27">
@@ -1000,27 +990,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreIce</t>
+          <t xml:space="preserve">tourmaline</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰核寶石</t>
+          <t xml:space="preserve">黑碧璽</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌨️</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgIce</t>
+          <t xml:space="preserve">dmgVsDark</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰屬性傷害提升%</t>
+          <t xml:space="preserve">對暗屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F28">
@@ -1040,27 +1030,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLightning</t>
+          <t xml:space="preserve">coreFire</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷核寶石</t>
+          <t xml:space="preserve">焰核寶石</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLightning</t>
+          <t xml:space="preserve">elemDmgFire</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷屬性傷害提升%</t>
+          <t xml:space="preserve">火屬性傷害提升%</t>
         </is>
       </c>
       <c r="F29">
@@ -1080,27 +1070,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">corePoison</t>
+          <t xml:space="preserve">coreIce</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒核寶石</t>
+          <t xml:space="preserve">冰核寶石</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦠</t>
+          <t xml:space="preserve">🌨️</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgPoison</t>
+          <t xml:space="preserve">elemDmgIce</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒屬性傷害提升%</t>
+          <t xml:space="preserve">冰屬性傷害提升%</t>
         </is>
       </c>
       <c r="F30">
@@ -1120,27 +1110,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLight</t>
+          <t xml:space="preserve">coreLightning</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖核寶石</t>
+          <t xml:space="preserve">雷核寶石</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLight</t>
+          <t xml:space="preserve">elemDmgLightning</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖屬性傷害提升%</t>
+          <t xml:space="preserve">雷屬性傷害提升%</t>
         </is>
       </c>
       <c r="F31">
@@ -1160,27 +1150,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreDark</t>
+          <t xml:space="preserve">corePoison</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗核寶石</t>
+          <t xml:space="preserve">毒核寶石</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌚</t>
+          <t xml:space="preserve">🦠</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgDark</t>
+          <t xml:space="preserve">elemDmgPoison</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗屬性傷害提升%</t>
+          <t xml:space="preserve">毒屬性傷害提升%</t>
         </is>
       </c>
       <c r="F32">
@@ -1200,31 +1190,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardFire</t>
+          <t xml:space="preserve">coreLight</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">火抗寶石</t>
+          <t xml:space="preserve">聖核寶石</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧯</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">resFire</t>
+          <t xml:space="preserve">elemDmgLight</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰抗性%</t>
+          <t xml:space="preserve">聖屬性傷害提升%</t>
         </is>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1240,31 +1230,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardIce</t>
+          <t xml:space="preserve">coreDark</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰抗寶石</t>
+          <t xml:space="preserve">暗核寶石</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">🌚</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">resIce</t>
+          <t xml:space="preserve">elemDmgDark</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜抗性%</t>
+          <t xml:space="preserve">暗屬性傷害提升%</t>
         </is>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1280,27 +1270,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLightning</t>
+          <t xml:space="preserve">wardFire</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">電抗寶石</t>
+          <t xml:space="preserve">火抗寶石</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔌</t>
+          <t xml:space="preserve">🧯</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLightning</t>
+          <t xml:space="preserve">resFire</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電抗性%</t>
+          <t xml:space="preserve">火焰抗性%</t>
         </is>
       </c>
       <c r="F35">
@@ -1320,27 +1310,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardPoison</t>
+          <t xml:space="preserve">wardIce</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒抗寶石</t>
+          <t xml:space="preserve">冰抗寶石</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">💊</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">resPoison</t>
+          <t xml:space="preserve">resIce</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">劇毒抗性%</t>
+          <t xml:space="preserve">冰霜抗性%</t>
         </is>
       </c>
       <c r="F36">
@@ -1360,27 +1350,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardDark</t>
+          <t xml:space="preserve">wardLightning</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗抗寶石</t>
+          <t xml:space="preserve">電抗寶石</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕯️</t>
+          <t xml:space="preserve">🔌</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">resDark</t>
+          <t xml:space="preserve">resLightning</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影抗性%</t>
+          <t xml:space="preserve">雷電抗性%</t>
         </is>
       </c>
       <c r="F37">
@@ -1400,27 +1390,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLight</t>
+          <t xml:space="preserve">wardPoison</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖抗寶石</t>
+          <t xml:space="preserve">毒抗寶石</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕶️</t>
+          <t xml:space="preserve">💊</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLight</t>
+          <t xml:space="preserve">resPoison</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖光抗性%</t>
+          <t xml:space="preserve">劇毒抗性%</t>
         </is>
       </c>
       <c r="F38">
@@ -1440,38 +1430,118 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t xml:space="preserve">wardDark</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗抗寶石</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕯️</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resDark</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗影抗性%</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardLight</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖抗寶石</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕶️</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLight</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖光抗性%</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t xml:space="preserve">wardAll</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性寶石</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">🌈</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">resAll</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性%</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="F41">
         <v>1</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>

--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -254,7 +254,7 @@
         </is>
       </c>
       <c r="F7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -580,33 +580,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">jade</t>
+          <t xml:space="preserve">piercePhys</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">翡翠</t>
+          <t xml:space="preserve">穿甲寶石</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟩</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">tenacity</t>
+          <t xml:space="preserve">pPen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">韌性%</t>
+          <t xml:space="preserve">物理穿透%</t>
         </is>
       </c>
       <c r="F17">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -615,33 +620,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">turquoise</t>
+          <t xml:space="preserve">pierceMagic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">綠松石</t>
+          <t xml:space="preserve">穿魔寶石</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟦</t>
+          <t xml:space="preserve">🪄</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockRate</t>
+          <t xml:space="preserve">mPen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋率%</t>
+          <t xml:space="preserve">魔法穿透%</t>
         </is>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -650,27 +660,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">agate</t>
+          <t xml:space="preserve">jade</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">瑪瑙</t>
+          <t xml:space="preserve">翡翠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
+          <t xml:space="preserve">🟩</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockDmgRed</t>
+          <t xml:space="preserve">tenacity</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋減傷%</t>
+          <t xml:space="preserve">韌性%</t>
         </is>
       </c>
       <c r="F19">
@@ -685,31 +695,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pearl</t>
+          <t xml:space="preserve">turquoise</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">珍珠</t>
+          <t xml:space="preserve">綠松石</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">🤍</t>
+          <t xml:space="preserve">🟦</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldEff</t>
+          <t xml:space="preserve">blockRate</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾效率%</t>
+          <t xml:space="preserve">格擋率%</t>
         </is>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -720,31 +730,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">malachite</t>
+          <t xml:space="preserve">agate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">孔雀石</t>
+          <t xml:space="preserve">瑪瑙</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">💚</t>
+          <t xml:space="preserve">🟤</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pRes</t>
+          <t xml:space="preserve">blockDmgRed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理抗性%</t>
+          <t xml:space="preserve">格擋減傷%</t>
         </is>
       </c>
       <c r="F21">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -755,31 +765,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">fluorite</t>
+          <t xml:space="preserve">pearl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">螢石</t>
+          <t xml:space="preserve">珍珠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">💙</t>
+          <t xml:space="preserve">🤍</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">mRes</t>
+          <t xml:space="preserve">shieldEff</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法抗性%</t>
+          <t xml:space="preserve">護盾效率%</t>
         </is>
       </c>
       <c r="F22">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -790,38 +800,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">spinel</t>
+          <t xml:space="preserve">malachite</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">尖晶石</t>
+          <t xml:space="preserve">孔雀石</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
+          <t xml:space="preserve">💚</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsFire</t>
+          <t xml:space="preserve">pRes</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">對火屬性敵人傷害%</t>
+          <t xml:space="preserve">物理抗性%</t>
         </is>
       </c>
       <c r="F23">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -830,38 +835,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">aquamarine</t>
+          <t xml:space="preserve">fluorite</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">海藍寶石</t>
+          <t xml:space="preserve">螢石</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">💙</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsIce</t>
+          <t xml:space="preserve">mRes</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">對冰屬性敵人傷害%</t>
+          <t xml:space="preserve">魔法抗性%</t>
         </is>
       </c>
       <c r="F24">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -870,31 +870,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">amazonite</t>
+          <t xml:space="preserve">spinel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">天河石</t>
+          <t xml:space="preserve">尖晶石</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLightning</t>
+          <t xml:space="preserve">dmgVsFire</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">對雷屬性敵人傷害%</t>
+          <t xml:space="preserve">對火屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F25">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -910,31 +910,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">peridot</t>
+          <t xml:space="preserve">aquamarine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">橄欖石</t>
+          <t xml:space="preserve">海藍寶石</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">☠️</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsPoison</t>
+          <t xml:space="preserve">dmgVsIce</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">對毒屬性敵人傷害%</t>
+          <t xml:space="preserve">對冰屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F26">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -950,31 +950,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">citrine</t>
+          <t xml:space="preserve">amazonite</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃水晶</t>
+          <t xml:space="preserve">天河石</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsLight</t>
+          <t xml:space="preserve">dmgVsLightning</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">對聖屬性敵人傷害%</t>
+          <t xml:space="preserve">對雷屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F27">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -990,31 +990,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">tourmaline</t>
+          <t xml:space="preserve">peridot</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">黑碧璽</t>
+          <t xml:space="preserve">橄欖石</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">☠️</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmgVsDark</t>
+          <t xml:space="preserve">dmgVsPoison</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">對暗屬性敵人傷害%</t>
+          <t xml:space="preserve">對毒屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F28">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1030,31 +1030,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreFire</t>
+          <t xml:space="preserve">citrine</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">焰核寶石</t>
+          <t xml:space="preserve">黃水晶</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgFire</t>
+          <t xml:space="preserve">dmgVsLight</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">火屬性傷害提升%</t>
+          <t xml:space="preserve">對聖屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F29">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1070,31 +1070,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreIce</t>
+          <t xml:space="preserve">tourmaline</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰核寶石</t>
+          <t xml:space="preserve">黑碧璽</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌨️</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgIce</t>
+          <t xml:space="preserve">dmgVsDark</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰屬性傷害提升%</t>
+          <t xml:space="preserve">對暗屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F30">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1110,31 +1110,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLightning</t>
+          <t xml:space="preserve">coreFire</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷核寶石</t>
+          <t xml:space="preserve">焰核寶石</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLightning</t>
+          <t xml:space="preserve">elemDmgFire</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷屬性傷害提升%</t>
+          <t xml:space="preserve">火屬性傷害提升%</t>
         </is>
       </c>
       <c r="F31">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1150,31 +1150,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">corePoison</t>
+          <t xml:space="preserve">coreIce</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒核寶石</t>
+          <t xml:space="preserve">冰核寶石</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦠</t>
+          <t xml:space="preserve">🌨️</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgPoison</t>
+          <t xml:space="preserve">elemDmgIce</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒屬性傷害提升%</t>
+          <t xml:space="preserve">冰屬性傷害提升%</t>
         </is>
       </c>
       <c r="F32">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1190,31 +1190,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLight</t>
+          <t xml:space="preserve">coreLightning</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖核寶石</t>
+          <t xml:space="preserve">雷核寶石</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLight</t>
+          <t xml:space="preserve">elemDmgLightning</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖屬性傷害提升%</t>
+          <t xml:space="preserve">雷屬性傷害提升%</t>
         </is>
       </c>
       <c r="F33">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1230,31 +1230,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreDark</t>
+          <t xml:space="preserve">corePoison</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗核寶石</t>
+          <t xml:space="preserve">毒核寶石</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌚</t>
+          <t xml:space="preserve">🦠</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgDark</t>
+          <t xml:space="preserve">elemDmgPoison</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗屬性傷害提升%</t>
+          <t xml:space="preserve">毒屬性傷害提升%</t>
         </is>
       </c>
       <c r="F34">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1270,31 +1270,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardFire</t>
+          <t xml:space="preserve">coreLight</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">火抗寶石</t>
+          <t xml:space="preserve">聖核寶石</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧯</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">resFire</t>
+          <t xml:space="preserve">elemDmgLight</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰抗性%</t>
+          <t xml:space="preserve">聖屬性傷害提升%</t>
         </is>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1310,31 +1310,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardIce</t>
+          <t xml:space="preserve">coreDark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰抗寶石</t>
+          <t xml:space="preserve">暗核寶石</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">🌚</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">resIce</t>
+          <t xml:space="preserve">elemDmgDark</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜抗性%</t>
+          <t xml:space="preserve">暗屬性傷害提升%</t>
         </is>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1350,27 +1350,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLightning</t>
+          <t xml:space="preserve">wardFire</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">電抗寶石</t>
+          <t xml:space="preserve">火抗寶石</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔌</t>
+          <t xml:space="preserve">🧯</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLightning</t>
+          <t xml:space="preserve">resFire</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電抗性%</t>
+          <t xml:space="preserve">火焰抗性%</t>
         </is>
       </c>
       <c r="F37">
@@ -1390,27 +1390,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardPoison</t>
+          <t xml:space="preserve">wardIce</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒抗寶石</t>
+          <t xml:space="preserve">冰抗寶石</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">💊</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">resPoison</t>
+          <t xml:space="preserve">resIce</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">劇毒抗性%</t>
+          <t xml:space="preserve">冰霜抗性%</t>
         </is>
       </c>
       <c r="F38">
@@ -1430,27 +1430,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardDark</t>
+          <t xml:space="preserve">wardLightning</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗抗寶石</t>
+          <t xml:space="preserve">電抗寶石</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕯️</t>
+          <t xml:space="preserve">🔌</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">resDark</t>
+          <t xml:space="preserve">resLightning</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影抗性%</t>
+          <t xml:space="preserve">雷電抗性%</t>
         </is>
       </c>
       <c r="F39">
@@ -1470,27 +1470,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLight</t>
+          <t xml:space="preserve">wardPoison</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖抗寶石</t>
+          <t xml:space="preserve">毒抗寶石</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕶️</t>
+          <t xml:space="preserve">💊</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLight</t>
+          <t xml:space="preserve">resPoison</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖光抗性%</t>
+          <t xml:space="preserve">劇毒抗性%</t>
         </is>
       </c>
       <c r="F40">
@@ -1510,38 +1510,118 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t xml:space="preserve">wardDark</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗抗寶石</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕯️</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resDark</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗影抗性%</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardLight</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖抗寶石</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕶️</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLight</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖光抗性%</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t xml:space="preserve">wardAll</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性寶石</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">🌈</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t xml:space="preserve">resAll</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性%</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="F43">
         <v>1</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>

--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -1110,27 +1110,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreFire</t>
+          <t xml:space="preserve">tigerEye</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">焰核寶石</t>
+          <t xml:space="preserve">虎眼石</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgFire</t>
+          <t xml:space="preserve">dmgVsEarth</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">火屬性傷害提升%</t>
+          <t xml:space="preserve">對地屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F31">
@@ -1150,27 +1150,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreIce</t>
+          <t xml:space="preserve">coreFire</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰核寶石</t>
+          <t xml:space="preserve">焰核寶石</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌨️</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgIce</t>
+          <t xml:space="preserve">elemDmgFire</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰屬性傷害提升%</t>
+          <t xml:space="preserve">火屬性傷害提升%</t>
         </is>
       </c>
       <c r="F32">
@@ -1190,27 +1190,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLightning</t>
+          <t xml:space="preserve">coreIce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷核寶石</t>
+          <t xml:space="preserve">冰核寶石</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">🌨️</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLightning</t>
+          <t xml:space="preserve">elemDmgIce</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷屬性傷害提升%</t>
+          <t xml:space="preserve">冰屬性傷害提升%</t>
         </is>
       </c>
       <c r="F33">
@@ -1230,27 +1230,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">corePoison</t>
+          <t xml:space="preserve">coreLightning</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒核寶石</t>
+          <t xml:space="preserve">雷核寶石</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦠</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgPoison</t>
+          <t xml:space="preserve">elemDmgLightning</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒屬性傷害提升%</t>
+          <t xml:space="preserve">雷屬性傷害提升%</t>
         </is>
       </c>
       <c r="F34">
@@ -1270,27 +1270,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLight</t>
+          <t xml:space="preserve">corePoison</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖核寶石</t>
+          <t xml:space="preserve">毒核寶石</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🦠</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLight</t>
+          <t xml:space="preserve">elemDmgPoison</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖屬性傷害提升%</t>
+          <t xml:space="preserve">毒屬性傷害提升%</t>
         </is>
       </c>
       <c r="F35">
@@ -1310,27 +1310,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreDark</t>
+          <t xml:space="preserve">coreLight</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗核寶石</t>
+          <t xml:space="preserve">聖核寶石</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌚</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgDark</t>
+          <t xml:space="preserve">elemDmgLight</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗屬性傷害提升%</t>
+          <t xml:space="preserve">聖屬性傷害提升%</t>
         </is>
       </c>
       <c r="F36">
@@ -1350,31 +1350,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardFire</t>
+          <t xml:space="preserve">coreDark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">火抗寶石</t>
+          <t xml:space="preserve">暗核寶石</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧯</t>
+          <t xml:space="preserve">🌚</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">resFire</t>
+          <t xml:space="preserve">elemDmgDark</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰抗性%</t>
+          <t xml:space="preserve">暗屬性傷害提升%</t>
         </is>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1390,31 +1390,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardIce</t>
+          <t xml:space="preserve">coreEarth</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰抗寶石</t>
+          <t xml:space="preserve">地核寶石</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">🏔️</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">resIce</t>
+          <t xml:space="preserve">elemDmgEarth</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜抗性%</t>
+          <t xml:space="preserve">地屬性傷害提升%</t>
         </is>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1430,27 +1430,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLightning</t>
+          <t xml:space="preserve">wardFire</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">電抗寶石</t>
+          <t xml:space="preserve">火抗寶石</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔌</t>
+          <t xml:space="preserve">🧯</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLightning</t>
+          <t xml:space="preserve">resFire</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電抗性%</t>
+          <t xml:space="preserve">火焰抗性%</t>
         </is>
       </c>
       <c r="F39">
@@ -1470,27 +1470,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardPoison</t>
+          <t xml:space="preserve">wardIce</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒抗寶石</t>
+          <t xml:space="preserve">冰抗寶石</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">💊</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">resPoison</t>
+          <t xml:space="preserve">resIce</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">劇毒抗性%</t>
+          <t xml:space="preserve">冰霜抗性%</t>
         </is>
       </c>
       <c r="F40">
@@ -1510,27 +1510,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardDark</t>
+          <t xml:space="preserve">wardLightning</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗抗寶石</t>
+          <t xml:space="preserve">電抗寶石</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕯️</t>
+          <t xml:space="preserve">🔌</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">resDark</t>
+          <t xml:space="preserve">resLightning</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影抗性%</t>
+          <t xml:space="preserve">雷電抗性%</t>
         </is>
       </c>
       <c r="F41">
@@ -1550,27 +1550,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLight</t>
+          <t xml:space="preserve">wardPoison</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖抗寶石</t>
+          <t xml:space="preserve">毒抗寶石</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕶️</t>
+          <t xml:space="preserve">💊</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLight</t>
+          <t xml:space="preserve">resPoison</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖光抗性%</t>
+          <t xml:space="preserve">劇毒抗性%</t>
         </is>
       </c>
       <c r="F42">
@@ -1590,38 +1590,158 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t xml:space="preserve">wardDark</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗抗寶石</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕯️</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resDark</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗影抗性%</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardLight</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖抗寶石</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕶️</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLight</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖光抗性%</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardEarth</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地抗寶石</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🧱</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resEarth</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大地抗性%</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t xml:space="preserve">wardAll</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性寶石</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t xml:space="preserve">🌈</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t xml:space="preserve">resAll</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性%</t>
         </is>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>

--- a/config/Excel/Gems.xlsx
+++ b/config/Excel/Gems.xlsx
@@ -1150,27 +1150,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreFire</t>
+          <t xml:space="preserve">moldavite</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">焰核寶石</t>
+          <t xml:space="preserve">捷克隕石</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgFire</t>
+          <t xml:space="preserve">dmgVsWind</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">火屬性傷害提升%</t>
+          <t xml:space="preserve">對風屬性敵人傷害%</t>
         </is>
       </c>
       <c r="F32">
@@ -1190,27 +1190,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreIce</t>
+          <t xml:space="preserve">coreFire</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰核寶石</t>
+          <t xml:space="preserve">焰核寶石</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌨️</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgIce</t>
+          <t xml:space="preserve">elemDmgFire</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰屬性傷害提升%</t>
+          <t xml:space="preserve">火屬性傷害提升%</t>
         </is>
       </c>
       <c r="F33">
@@ -1230,27 +1230,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLightning</t>
+          <t xml:space="preserve">coreIce</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷核寶石</t>
+          <t xml:space="preserve">冰核寶石</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">🌨️</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLightning</t>
+          <t xml:space="preserve">elemDmgIce</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷屬性傷害提升%</t>
+          <t xml:space="preserve">冰屬性傷害提升%</t>
         </is>
       </c>
       <c r="F34">
@@ -1270,27 +1270,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">corePoison</t>
+          <t xml:space="preserve">coreLightning</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒核寶石</t>
+          <t xml:space="preserve">雷核寶石</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">🦠</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgPoison</t>
+          <t xml:space="preserve">elemDmgLightning</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒屬性傷害提升%</t>
+          <t xml:space="preserve">雷屬性傷害提升%</t>
         </is>
       </c>
       <c r="F35">
@@ -1310,27 +1310,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreLight</t>
+          <t xml:space="preserve">corePoison</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖核寶石</t>
+          <t xml:space="preserve">毒核寶石</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌟</t>
+          <t xml:space="preserve">🦠</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgLight</t>
+          <t xml:space="preserve">elemDmgPoison</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖屬性傷害提升%</t>
+          <t xml:space="preserve">毒屬性傷害提升%</t>
         </is>
       </c>
       <c r="F36">
@@ -1350,27 +1350,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreDark</t>
+          <t xml:space="preserve">coreLight</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗核寶石</t>
+          <t xml:space="preserve">聖核寶石</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌚</t>
+          <t xml:space="preserve">🌟</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgDark</t>
+          <t xml:space="preserve">elemDmgLight</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗屬性傷害提升%</t>
+          <t xml:space="preserve">聖屬性傷害提升%</t>
         </is>
       </c>
       <c r="F37">
@@ -1390,27 +1390,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">coreEarth</t>
+          <t xml:space="preserve">coreDark</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">地核寶石</t>
+          <t xml:space="preserve">暗核寶石</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">🏔️</t>
+          <t xml:space="preserve">🌚</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">elemDmgEarth</t>
+          <t xml:space="preserve">elemDmgDark</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">地屬性傷害提升%</t>
+          <t xml:space="preserve">暗屬性傷害提升%</t>
         </is>
       </c>
       <c r="F38">
@@ -1430,31 +1430,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardFire</t>
+          <t xml:space="preserve">coreEarth</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">火抗寶石</t>
+          <t xml:space="preserve">地核寶石</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧯</t>
+          <t xml:space="preserve">🏔️</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">resFire</t>
+          <t xml:space="preserve">elemDmgEarth</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰抗性%</t>
+          <t xml:space="preserve">地屬性傷害提升%</t>
         </is>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1470,31 +1470,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardIce</t>
+          <t xml:space="preserve">coreWind</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰抗寶石</t>
+          <t xml:space="preserve">風核寶石</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">🌪️</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">resIce</t>
+          <t xml:space="preserve">elemDmgWind</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜抗性%</t>
+          <t xml:space="preserve">風屬性傷害提升%</t>
         </is>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1510,27 +1510,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLightning</t>
+          <t xml:space="preserve">wardFire</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">電抗寶石</t>
+          <t xml:space="preserve">火抗寶石</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔌</t>
+          <t xml:space="preserve">🧯</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLightning</t>
+          <t xml:space="preserve">resFire</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電抗性%</t>
+          <t xml:space="preserve">火焰抗性%</t>
         </is>
       </c>
       <c r="F41">
@@ -1550,27 +1550,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardPoison</t>
+          <t xml:space="preserve">wardIce</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒抗寶石</t>
+          <t xml:space="preserve">冰抗寶石</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">💊</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">resPoison</t>
+          <t xml:space="preserve">resIce</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">劇毒抗性%</t>
+          <t xml:space="preserve">冰霜抗性%</t>
         </is>
       </c>
       <c r="F42">
@@ -1590,27 +1590,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardDark</t>
+          <t xml:space="preserve">wardLightning</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗抗寶石</t>
+          <t xml:space="preserve">電抗寶石</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕯️</t>
+          <t xml:space="preserve">🔌</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">resDark</t>
+          <t xml:space="preserve">resLightning</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影抗性%</t>
+          <t xml:space="preserve">雷電抗性%</t>
         </is>
       </c>
       <c r="F43">
@@ -1630,27 +1630,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardLight</t>
+          <t xml:space="preserve">wardPoison</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖抗寶石</t>
+          <t xml:space="preserve">毒抗寶石</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕶️</t>
+          <t xml:space="preserve">💊</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">resLight</t>
+          <t xml:space="preserve">resPoison</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖光抗性%</t>
+          <t xml:space="preserve">劇毒抗性%</t>
         </is>
       </c>
       <c r="F44">
@@ -1670,27 +1670,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardEarth</t>
+          <t xml:space="preserve">wardDark</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">地抗寶石</t>
+          <t xml:space="preserve">暗抗寶石</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧱</t>
+          <t xml:space="preserve">🕯️</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">resEarth</t>
+          <t xml:space="preserve">resDark</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地抗性%</t>
+          <t xml:space="preserve">暗影抗性%</t>
         </is>
       </c>
       <c r="F45">
@@ -1710,38 +1710,158 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t xml:space="preserve">wardLight</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖抗寶石</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕶️</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resLight</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖光抗性%</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardEarth</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地抗寶石</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🧱</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resEarth</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大地抗性%</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wardWind</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風抗寶石</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resWind</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風抗性%</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t xml:space="preserve">wardAll</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性寶石</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t xml:space="preserve">🌈</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t xml:space="preserve">resAll</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">全屬性抗性%</t>
         </is>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
